--- a/excel/Kommune_Project_Controller_EVM_2026.xlsx
+++ b/excel/Kommune_Project_Controller_EVM_2026.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SHA-256: 92fc763990efd6279c1d58bbe4892449b076920f7ddc9ac6ef1733798c43299b</t>
+          <t>SHA-256: 3644944bd560c113679d5624006cb42fff782666c4a8b005af2201349df4a0c1</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>14.10.2026</t>
+          <t>18.10.2026</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E17" s="44" t="inlineStr">
         <is>
-          <t>Dato: 14.10.2026</t>
+          <t>Dato: 18.10.2026</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C18" s="43" t="inlineStr">
         <is>
-          <t>92fc763990efd6279c1d58bbe4892449...</t>
+          <t>3644944bd560c113679d5624006cb42f...</t>
         </is>
       </c>
       <c r="E18" s="44" t="inlineStr">
